--- a/public/templates/3_Litmus_Packages_Bulk_Template.xlsx
+++ b/public/templates/3_Litmus_Packages_Bulk_Template.xlsx
@@ -488,10 +488,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:M5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
-    <col width="123" customWidth="1" min="1" max="1"/>
+    <col width="206" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
     <col width="77" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
@@ -503,12 +503,13 @@
     <col width="115" customWidth="1" min="10" max="10"/>
     <col width="115" customWidth="1" min="11" max="11"/>
     <col width="51" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>INSTRUCTIONS: Bundle existing tests by providing comma-separated test names. Specify selling price and turnaround time.</t>
+          <t>INSTRUCTIONS: Bundle existing tests by providing comma-separated test names. Specify selling price and turnaround time. Optional 'displayOrder' sets the website priority (1 = shown first; 0 removes it).</t>
         </is>
       </c>
     </row>
@@ -573,6 +574,11 @@
           <t>image</t>
         </is>
       </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>displayOrder</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
@@ -635,6 +641,11 @@
           <t>OPTIONAL</t>
         </is>
       </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>OPTIONAL</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="22" customHeight="1">
       <c r="A4" s="5" t="inlineStr">
@@ -691,6 +702,9 @@
           <t>https://example.com/packages/dairy-standard.png</t>
         </is>
       </c>
+      <c r="M4" s="5" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
       <c r="A5" s="5" t="inlineStr">
@@ -743,10 +757,11 @@
         </is>
       </c>
       <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A1:M1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
